--- a/public/exports-from-60-with-coowners/29189986.xlsx
+++ b/public/exports-from-60-with-coowners/29189986.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -11539,12 +11539,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289828</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -11764,12 +11764,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189986.xlsx
+++ b/public/exports-from-60-with-coowners/29189986.xlsx
@@ -3154,12 +3154,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -11614,12 +11614,12 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -11764,12 +11764,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M160" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189986.xlsx
+++ b/public/exports-from-60-with-coowners/29189986.xlsx
@@ -11539,12 +11539,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289828</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
